--- a/URUVS/Datasheets/URUV/08.2024/August_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/08.2024/August_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\08.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF159F98-A8DB-455C-BDA5-54734143DD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3281DAC-00A0-48B1-A1BA-B654F8B7F3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="225">
   <si>
     <t>DATE</t>
   </si>
@@ -678,6 +678,42 @@
   </si>
   <si>
     <t>T1_FISHCHEETAGIRLZ</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_1STSHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
+  </si>
+  <si>
+    <t>MAXN_FISHWTH</t>
+  </si>
+  <si>
+    <t>TIME_1STFISHWTH</t>
+  </si>
+  <si>
+    <t>T1_FISHWTH</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1068,7 @@
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="21" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1313,18 +1349,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DL22"/>
+  <dimension ref="A1:DX22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" customWidth="1"/>
-    <col min="7" max="8" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="9" max="22" width="8.7265625" customWidth="1"/>
+    <col min="3" max="22" width="8.7265625" customWidth="1"/>
     <col min="23" max="29" width="8.7265625" style="1" customWidth="1"/>
     <col min="30" max="36" width="8.7265625" customWidth="1"/>
-    <col min="37" max="37" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.90625" customWidth="1"/>
+    <col min="38" max="38" width="8.7265625" customWidth="1"/>
     <col min="40" max="40" width="14.08984375" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="10.7265625" bestFit="1" customWidth="1"/>
@@ -1340,10 +1374,14 @@
     <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:116" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:128" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>196</v>
       </c>
@@ -1689,11 +1727,47 @@
       <c r="DK1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="DL1" s="28" t="s">
+      <c r="DL1" s="81" t="s">
+        <v>213</v>
+      </c>
+      <c r="DM1" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="DN1" s="59" t="s">
+        <v>215</v>
+      </c>
+      <c r="DO1" s="81" t="s">
+        <v>216</v>
+      </c>
+      <c r="DP1" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="DQ1" s="59" t="s">
+        <v>218</v>
+      </c>
+      <c r="DR1" s="81" t="s">
+        <v>219</v>
+      </c>
+      <c r="DS1" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="DT1" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="DU1" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="DV1" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="DW1" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="DX1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>197</v>
       </c>
@@ -1976,12 +2050,40 @@
       <c r="DI2" s="58"/>
       <c r="DJ2" s="71"/>
       <c r="DK2" s="33" t="str">
-        <f t="shared" ref="DK2:DK13" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="DL2" s="35"/>
+        <f t="shared" ref="DK2:DK22" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DL2" s="58"/>
+      <c r="DM2" s="71"/>
+      <c r="DN2" s="33" t="str">
+        <f t="shared" ref="DN2:DN22" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DO2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DP2" s="71">
+        <v>3.1087962962962963E-2</v>
+      </c>
+      <c r="DQ2" s="33">
+        <f t="shared" ref="DQ2:DQ22" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
+        <v>2.7615740740740739E-2</v>
+      </c>
+      <c r="DR2" s="58"/>
+      <c r="DS2" s="71"/>
+      <c r="DT2" s="33" t="str">
+        <f t="shared" ref="DT2:DT22" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DU2" s="58"/>
+      <c r="DV2" s="71"/>
+      <c r="DW2" s="33" t="str">
+        <f t="shared" ref="DW2:DW13" si="30">IF(DU2=0,"NA",DV2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DX2" s="35"/>
     </row>
-    <row r="3" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>197</v>
       </c>
@@ -1998,7 +2100,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F22" si="27">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F22" si="31">D3&amp;""&amp;E3</f>
         <v>E3</v>
       </c>
       <c r="G3" s="5">
@@ -2034,7 +2136,7 @@
         <v>3</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q22" si="28">J3-I3</f>
+        <f t="shared" ref="Q3:Q22" si="32">J3-I3</f>
         <v>7.6388888888888895E-2</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2065,7 +2167,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="29">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="33">SUM(W3:AB3)</f>
         <v>4.1805555555555554E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2096,7 +2198,7 @@
         <v>NA</v>
       </c>
       <c r="AO3" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP3" s="34">
         <v>5.6365740740740742E-3</v>
@@ -2148,7 +2250,7 @@
         <v>NA</v>
       </c>
       <c r="BM3" s="31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN3" s="34">
         <v>3.8888888888888888E-3</v>
@@ -2261,9 +2363,37 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL3" s="35"/>
+      <c r="DL3" s="31"/>
+      <c r="DM3" s="32"/>
+      <c r="DN3" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO3" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP3" s="34">
+        <v>2.6064814814814815E-2</v>
+      </c>
+      <c r="DQ3" s="33">
+        <f t="shared" si="28"/>
+        <v>2.2592592592592595E-2</v>
+      </c>
+      <c r="DR3" s="31"/>
+      <c r="DS3" s="32"/>
+      <c r="DT3" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU3" s="31"/>
+      <c r="DV3" s="32"/>
+      <c r="DW3" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX3" s="35"/>
     </row>
-    <row r="4" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>197</v>
       </c>
@@ -2280,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>E1</v>
       </c>
       <c r="G4" s="5">
@@ -2316,7 +2446,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.3611111111111127E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2345,7 +2475,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>5.6145833333333339E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2535,9 +2665,33 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL4" s="35"/>
+      <c r="DL4" s="31"/>
+      <c r="DM4" s="34"/>
+      <c r="DN4" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO4" s="31"/>
+      <c r="DP4" s="34"/>
+      <c r="DQ4" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR4" s="31"/>
+      <c r="DS4" s="34"/>
+      <c r="DT4" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU4" s="31"/>
+      <c r="DV4" s="34"/>
+      <c r="DW4" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX4" s="35"/>
     </row>
-    <row r="5" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>197</v>
       </c>
@@ -2554,7 +2708,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D2</v>
       </c>
       <c r="G5" s="5">
@@ -2590,7 +2744,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.2916666666666685E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2619,7 +2773,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>2.8333333333333332E-2</v>
       </c>
       <c r="AD5" s="20">
@@ -2819,9 +2973,41 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL5" s="35"/>
+      <c r="DL5" s="31"/>
+      <c r="DM5" s="32"/>
+      <c r="DN5" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO5" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP5" s="34">
+        <v>2.3229166666666665E-2</v>
+      </c>
+      <c r="DQ5" s="33">
+        <f t="shared" si="28"/>
+        <v>1.9166666666666665E-2</v>
+      </c>
+      <c r="DR5" s="31"/>
+      <c r="DS5" s="32"/>
+      <c r="DT5" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU5" s="31">
+        <v>1</v>
+      </c>
+      <c r="DV5" s="34">
+        <v>5.6134259259259262E-3</v>
+      </c>
+      <c r="DW5" s="33">
+        <f t="shared" si="30"/>
+        <v>1.5509259259259261E-3</v>
+      </c>
+      <c r="DX5" s="35"/>
     </row>
-    <row r="6" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>197</v>
       </c>
@@ -2838,7 +3024,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D3</v>
       </c>
       <c r="G6" s="5">
@@ -2874,7 +3060,7 @@
         <v>6</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.0833333333333304E-2</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -2909,7 +3095,7 @@
         <v>1.5277777777777779E-3</v>
       </c>
       <c r="AC6" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>7.6736111111111102E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -3107,9 +3293,41 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL6" s="35"/>
+      <c r="DL6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM6" s="34">
+        <v>3.4155092592592591E-2</v>
+      </c>
+      <c r="DN6" s="33">
+        <f t="shared" si="27"/>
+        <v>2.9826388888888888E-2</v>
+      </c>
+      <c r="DO6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP6" s="34">
+        <v>3.0682870370370371E-2</v>
+      </c>
+      <c r="DQ6" s="33">
+        <f t="shared" si="28"/>
+        <v>2.6354166666666668E-2</v>
+      </c>
+      <c r="DR6" s="31"/>
+      <c r="DS6" s="32"/>
+      <c r="DT6" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU6" s="31"/>
+      <c r="DV6" s="32"/>
+      <c r="DW6" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX6" s="35"/>
     </row>
-    <row r="7" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>197</v>
       </c>
@@ -3126,7 +3344,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L2</v>
       </c>
       <c r="G7" s="5">
@@ -3162,7 +3380,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.9166666666666663E-2</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -3191,7 +3409,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>5.631944444444445E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3389,9 +3607,37 @@
         <f t="shared" si="26"/>
         <v>6.6319444444444438E-3</v>
       </c>
-      <c r="DL7" s="35"/>
+      <c r="DL7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM7" s="34">
+        <v>3.3703703703703701E-2</v>
+      </c>
+      <c r="DN7" s="33">
+        <f t="shared" si="27"/>
+        <v>2.9004629629629627E-2</v>
+      </c>
+      <c r="DO7" s="31"/>
+      <c r="DP7" s="34"/>
+      <c r="DQ7" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR7" s="31"/>
+      <c r="DS7" s="34"/>
+      <c r="DT7" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU7" s="31"/>
+      <c r="DV7" s="34"/>
+      <c r="DW7" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX7" s="35"/>
     </row>
-    <row r="8" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>197</v>
       </c>
@@ -3408,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L1</v>
       </c>
       <c r="G8" s="5">
@@ -3444,7 +3690,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -3473,7 +3719,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>6.0960648148148153E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3558,7 +3804,7 @@
         <v>NA</v>
       </c>
       <c r="BM8" s="31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN8" s="34">
         <v>3.0138888888888889E-2</v>
@@ -3658,7 +3904,7 @@
         <v>NA</v>
       </c>
       <c r="DI8" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DJ8" s="70">
         <v>2.1030092592592593E-2</v>
@@ -3667,9 +3913,41 @@
         <f t="shared" si="26"/>
         <v>1.6250000000000001E-2</v>
       </c>
-      <c r="DL8" s="35"/>
+      <c r="DL8" s="31"/>
+      <c r="DM8" s="70"/>
+      <c r="DN8" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP8" s="70">
+        <v>3.0497685185185187E-2</v>
+      </c>
+      <c r="DQ8" s="33">
+        <f t="shared" si="28"/>
+        <v>2.5717592592592594E-2</v>
+      </c>
+      <c r="DR8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS8" s="70">
+        <v>2.2175925925925925E-2</v>
+      </c>
+      <c r="DT8" s="33">
+        <f t="shared" si="29"/>
+        <v>1.7395833333333333E-2</v>
+      </c>
+      <c r="DU8" s="31"/>
+      <c r="DV8" s="70"/>
+      <c r="DW8" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX8" s="35"/>
     </row>
-    <row r="9" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>197</v>
       </c>
@@ -3686,7 +3964,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L3</v>
       </c>
       <c r="G9" s="5">
@@ -3722,7 +4000,7 @@
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.8333333333333293E-2</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -3751,7 +4029,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>5.9305555555555556E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -3949,9 +4227,33 @@
         <f t="shared" si="26"/>
         <v>6.5972222222222213E-4</v>
       </c>
-      <c r="DL9" s="35"/>
+      <c r="DL9" s="31"/>
+      <c r="DM9" s="56"/>
+      <c r="DN9" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO9" s="31"/>
+      <c r="DP9" s="56"/>
+      <c r="DQ9" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR9" s="31"/>
+      <c r="DS9" s="56"/>
+      <c r="DT9" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU9" s="31"/>
+      <c r="DV9" s="56"/>
+      <c r="DW9" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX9" s="35"/>
     </row>
-    <row r="10" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>197</v>
       </c>
@@ -3968,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D1</v>
       </c>
       <c r="G10" s="5">
@@ -4004,7 +4306,7 @@
         <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.6944444444444409E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -4033,7 +4335,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.1331018518518517E-2</v>
       </c>
       <c r="AD10" s="20">
@@ -4044,7 +4346,7 @@
         <f t="shared" si="0"/>
         <v>3.681712962962963E-2</v>
       </c>
-      <c r="AG10" s="87">
+      <c r="AG10" s="21">
         <v>70</v>
       </c>
       <c r="AH10" s="21">
@@ -4221,9 +4523,37 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL10" s="35"/>
+      <c r="DL10" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM10" s="34">
+        <v>2.6620370370370371E-2</v>
+      </c>
+      <c r="DN10" s="33">
+        <f t="shared" si="27"/>
+        <v>2.2106481481481484E-2</v>
+      </c>
+      <c r="DO10" s="31"/>
+      <c r="DP10" s="34"/>
+      <c r="DQ10" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR10" s="31"/>
+      <c r="DS10" s="34"/>
+      <c r="DT10" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU10" s="31"/>
+      <c r="DV10" s="34"/>
+      <c r="DW10" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX10" s="35"/>
     </row>
-    <row r="11" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>197</v>
       </c>
@@ -4240,7 +4570,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D4</v>
       </c>
       <c r="G11" s="5">
@@ -4276,7 +4606,7 @@
         <v>5</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>8.6111111111111083E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -4309,7 +4639,7 @@
       </c>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>7.0300925925925919E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4499,9 +4829,41 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL11" s="35"/>
+      <c r="DL11" s="31"/>
+      <c r="DM11" s="34"/>
+      <c r="DN11" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO11" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP11" s="34">
+        <v>2.1342592592592594E-2</v>
+      </c>
+      <c r="DQ11" s="33">
+        <f t="shared" si="28"/>
+        <v>1.7164351851851854E-2</v>
+      </c>
+      <c r="DR11" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS11" s="34">
+        <v>4.0972222222222222E-2</v>
+      </c>
+      <c r="DT11" s="33">
+        <f t="shared" si="29"/>
+        <v>3.6793981481481483E-2</v>
+      </c>
+      <c r="DU11" s="31"/>
+      <c r="DV11" s="34"/>
+      <c r="DW11" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX11" s="35"/>
     </row>
-    <row r="12" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>197</v>
       </c>
@@ -4518,7 +4880,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L6</v>
       </c>
       <c r="G12" s="5">
@@ -4554,7 +4916,7 @@
         <v>4</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>8.4722222222222199E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -4585,7 +4947,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>6.9004629629629638E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4783,9 +5145,37 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL12" s="35"/>
+      <c r="DL12" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM12" s="70">
+        <v>2.3379629629629629E-2</v>
+      </c>
+      <c r="DN12" s="33">
+        <f t="shared" si="27"/>
+        <v>1.9189814814814812E-2</v>
+      </c>
+      <c r="DO12" s="31"/>
+      <c r="DP12" s="70"/>
+      <c r="DQ12" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR12" s="31"/>
+      <c r="DS12" s="70"/>
+      <c r="DT12" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU12" s="31"/>
+      <c r="DV12" s="70"/>
+      <c r="DW12" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX12" s="35"/>
     </row>
-    <row r="13" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>197</v>
       </c>
@@ -4802,7 +5192,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D5</v>
       </c>
       <c r="G13" s="5">
@@ -4838,7 +5228,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.2916666666666685E-2</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -4863,7 +5253,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD13" s="20"/>
@@ -5033,9 +5423,33 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL13" s="35"/>
+      <c r="DL13" s="31"/>
+      <c r="DM13" s="32"/>
+      <c r="DN13" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO13" s="31"/>
+      <c r="DP13" s="32"/>
+      <c r="DQ13" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR13" s="31"/>
+      <c r="DS13" s="32"/>
+      <c r="DT13" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU13" s="31"/>
+      <c r="DV13" s="32"/>
+      <c r="DW13" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX13" s="35"/>
     </row>
-    <row r="14" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>197</v>
       </c>
@@ -5052,7 +5466,7 @@
         <v>5</v>
       </c>
       <c r="F14" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L5</v>
       </c>
       <c r="G14" s="5">
@@ -5088,7 +5502,7 @@
         <v>3</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>7.0833333333333304E-2</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -5117,7 +5531,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>5.0659722222222217E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -5127,7 +5541,7 @@
         <v>3.9814814814814817E-3</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="30">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="34">AC14-AD14-AE14</f>
         <v>4.1932870370370363E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -5138,33 +5552,33 @@
       </c>
       <c r="AI14" s="22"/>
       <c r="AJ14" s="29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK14" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" s="31"/>
       <c r="AM14" s="32"/>
       <c r="AN14" s="33" t="str">
-        <f t="shared" ref="AN14:AN22" si="31">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="35">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="32">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="36">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT22" si="33">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="37">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW22" si="34">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="38">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5186,43 +5600,43 @@
         <v>2.8958333333333332E-2</v>
       </c>
       <c r="BF14" s="33">
-        <f t="shared" ref="BF14:BF22" si="35">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF22" si="39">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>2.4212962962962964E-2</v>
       </c>
       <c r="BG14" s="31"/>
       <c r="BH14" s="32"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI22" si="36">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="40">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="34"/>
       <c r="BL14" s="33" t="str">
-        <f t="shared" ref="BL14:BL22" si="37">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="41">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BM14" s="31"/>
       <c r="BN14" s="34"/>
       <c r="BO14" s="33" t="str">
-        <f t="shared" ref="BO14:BO22" si="38">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="42">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR22" si="39">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="43">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="32"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU22" si="40">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU22" si="44">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BV14" s="31"/>
       <c r="BW14" s="34"/>
       <c r="BX14" s="33" t="str">
-        <f t="shared" ref="BX14:BX22" si="41">IF(BV14=0,"NA",BW14-$AD14)</f>
+        <f t="shared" ref="BX14:BX22" si="45">IF(BV14=0,"NA",BW14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BY14" s="31"/>
@@ -5295,11 +5709,15 @@
         <f t="shared" si="24"/>
         <v>3.4988425925925923E-2</v>
       </c>
-      <c r="DF14" s="31"/>
-      <c r="DG14" s="32"/>
-      <c r="DH14" s="33" t="str">
+      <c r="DF14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG14" s="34">
+        <v>1.0810185185185185E-2</v>
+      </c>
+      <c r="DH14" s="33">
         <f t="shared" si="25"/>
-        <v>NA</v>
+        <v>6.0648148148148145E-3</v>
       </c>
       <c r="DI14" s="31">
         <v>5</v>
@@ -5308,12 +5726,44 @@
         <v>3.3321759259259259E-2</v>
       </c>
       <c r="DK14" s="33">
-        <f t="shared" ref="DK14:DK22" si="42">IF(DI14=0,"NA",DJ14-$AD14)</f>
+        <f t="shared" si="26"/>
         <v>2.8576388888888887E-2</v>
       </c>
-      <c r="DL14" s="35"/>
+      <c r="DL14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM14" s="34">
+        <v>1.6446759259259258E-2</v>
+      </c>
+      <c r="DN14" s="33">
+        <f t="shared" si="27"/>
+        <v>1.1701388888888888E-2</v>
+      </c>
+      <c r="DO14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP14" s="34">
+        <v>5.6712962962962967E-3</v>
+      </c>
+      <c r="DQ14" s="33">
+        <f t="shared" si="28"/>
+        <v>9.2592592592592639E-4</v>
+      </c>
+      <c r="DR14" s="31"/>
+      <c r="DS14" s="34"/>
+      <c r="DT14" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU14" s="31"/>
+      <c r="DV14" s="34"/>
+      <c r="DW14" s="33" t="str">
+        <f t="shared" ref="DW14:DW22" si="46">IF(DU14=0,"NA",DV14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="DX14" s="35"/>
     </row>
-    <row r="15" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>197</v>
       </c>
@@ -5330,7 +5780,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L4</v>
       </c>
       <c r="G15" s="5">
@@ -5366,7 +5816,7 @@
         <v>4</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.8333333333333348E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -5391,13 +5841,13 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD15" s="20"/>
       <c r="AE15" s="20"/>
       <c r="AF15" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AG15" s="21"/>
@@ -5408,25 +5858,25 @@
       <c r="AL15" s="31"/>
       <c r="AM15" s="34"/>
       <c r="AN15" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO15" s="31"/>
       <c r="AP15" s="32"/>
       <c r="AQ15" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5444,43 +5894,43 @@
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
       <c r="BH15" s="32"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31"/>
       <c r="BK15" s="34"/>
       <c r="BL15" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="31"/>
       <c r="BN15" s="32"/>
       <c r="BO15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="32"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV15" s="31"/>
       <c r="BW15" s="34"/>
       <c r="BX15" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BY15" s="31"/>
@@ -5558,12 +6008,36 @@
       <c r="DI15" s="31"/>
       <c r="DJ15" s="32"/>
       <c r="DK15" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL15" s="35"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL15" s="31"/>
+      <c r="DM15" s="32"/>
+      <c r="DN15" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO15" s="31"/>
+      <c r="DP15" s="32"/>
+      <c r="DQ15" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR15" s="31"/>
+      <c r="DS15" s="32"/>
+      <c r="DT15" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU15" s="31"/>
+      <c r="DV15" s="32"/>
+      <c r="DW15" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX15" s="35"/>
     </row>
-    <row r="16" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>197</v>
       </c>
@@ -5580,7 +6054,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D6</v>
       </c>
       <c r="G16" s="5">
@@ -5616,7 +6090,7 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.7638888888888906E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -5645,7 +6119,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>3.9571759259259258E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -5653,7 +6127,7 @@
       </c>
       <c r="AE16" s="20"/>
       <c r="AF16" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3.5243055555555555E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -5663,30 +6137,34 @@
         <v>50</v>
       </c>
       <c r="AI16" s="22"/>
-      <c r="AJ16" s="29"/>
-      <c r="AK16" s="30"/>
+      <c r="AJ16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="30">
+        <v>0</v>
+      </c>
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -5704,43 +6182,43 @@
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
       <c r="BI16" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
       <c r="BL16" s="56" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM16" s="31"/>
       <c r="BN16" s="34"/>
       <c r="BO16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31"/>
       <c r="BT16" s="32"/>
       <c r="BU16" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV16" s="31"/>
       <c r="BW16" s="56"/>
       <c r="BX16" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BY16" s="31"/>
@@ -5818,12 +6296,40 @@
       <c r="DI16" s="31"/>
       <c r="DJ16" s="34"/>
       <c r="DK16" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL16" s="35"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL16" s="31"/>
+      <c r="DM16" s="34"/>
+      <c r="DN16" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO16" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP16" s="34">
+        <v>6.5856481481481478E-3</v>
+      </c>
+      <c r="DQ16" s="33">
+        <f t="shared" si="28"/>
+        <v>2.2569444444444442E-3</v>
+      </c>
+      <c r="DR16" s="31"/>
+      <c r="DS16" s="34"/>
+      <c r="DT16" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU16" s="31"/>
+      <c r="DV16" s="34"/>
+      <c r="DW16" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX16" s="35"/>
     </row>
-    <row r="17" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>197</v>
       </c>
@@ -5840,7 +6346,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>D5</v>
       </c>
       <c r="G17" s="5">
@@ -5876,7 +6382,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -5907,7 +6413,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.1377314814814811E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -5915,7 +6421,7 @@
       </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3.6238425925925924E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -5934,25 +6440,25 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -5974,37 +6480,37 @@
         <v>1.0462962962962962E-2</v>
       </c>
       <c r="BF17" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>5.3240740740740731E-3</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31"/>
       <c r="BK17" s="34"/>
       <c r="BL17" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31"/>
       <c r="BT17" s="34"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="31">
@@ -6014,7 +6520,7 @@
         <v>6.7592592592592591E-3</v>
       </c>
       <c r="BX17" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>1.6203703703703701E-3</v>
       </c>
       <c r="BY17" s="31"/>
@@ -6092,12 +6598,44 @@
       <c r="DI17" s="31"/>
       <c r="DJ17" s="34"/>
       <c r="DK17" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL17" s="35"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL17" s="31">
+        <v>3</v>
+      </c>
+      <c r="DM17" s="34">
+        <v>5.138888888888889E-3</v>
+      </c>
+      <c r="DN17" s="33">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="DO17" s="31">
+        <v>2</v>
+      </c>
+      <c r="DP17" s="34">
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="DQ17" s="33">
+        <f t="shared" si="28"/>
+        <v>1.1111111111111113E-3</v>
+      </c>
+      <c r="DR17" s="31"/>
+      <c r="DS17" s="34"/>
+      <c r="DT17" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU17" s="31"/>
+      <c r="DV17" s="34"/>
+      <c r="DW17" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX17" s="35"/>
     </row>
-    <row r="18" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>197</v>
       </c>
@@ -6114,7 +6652,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>L4</v>
       </c>
       <c r="G18" s="5">
@@ -6150,7 +6688,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>9.9305555555555536E-2</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -6181,7 +6719,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.2268518518518518E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6189,7 +6727,7 @@
       </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3.8483796296296294E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6208,34 +6746,30 @@
       <c r="AL18" s="31"/>
       <c r="AM18" s="34"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="31"/>
-        <v>NA</v>
-      </c>
-      <c r="AO18" s="31">
-        <v>2</v>
+        <f t="shared" si="35"/>
+        <v>NA</v>
+      </c>
+      <c r="AO18" s="87">
+        <v>4.1087962962962962E-3</v>
       </c>
       <c r="AP18" s="34">
         <v>6.4004629629629628E-3</v>
       </c>
       <c r="AQ18" s="33">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2.6157407407407405E-3</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="AU18" s="31">
-        <v>1</v>
-      </c>
-      <c r="AV18" s="34">
-        <v>3.0254629629629631E-2</v>
-      </c>
-      <c r="AW18" s="33">
-        <f t="shared" si="34"/>
-        <v>2.6469907407407407E-2</v>
+        <f t="shared" si="37"/>
+        <v>NA</v>
+      </c>
+      <c r="AU18" s="31"/>
+      <c r="AV18" s="34"/>
+      <c r="AW18" s="33" t="str">
+        <f t="shared" si="38"/>
+        <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
       <c r="AY18" s="34"/>
@@ -6260,19 +6794,19 @@
         <v>1.3020833333333334E-2</v>
       </c>
       <c r="BF18" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>9.2361111111111116E-3</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31"/>
       <c r="BK18" s="34"/>
       <c r="BL18" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="31">
@@ -6282,25 +6816,25 @@
         <v>4.6412037037037038E-3</v>
       </c>
       <c r="BO18" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>8.564814814814815E-4</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31"/>
       <c r="BT18" s="34"/>
       <c r="BU18" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV18" s="31"/>
       <c r="BW18" s="32"/>
       <c r="BX18" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BY18" s="31"/>
@@ -6369,21 +6903,57 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF18" s="31"/>
-      <c r="DG18" s="34"/>
-      <c r="DH18" s="33" t="str">
+      <c r="DF18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG18" s="34">
+        <v>1.238425925925926E-2</v>
+      </c>
+      <c r="DH18" s="33">
         <f t="shared" si="25"/>
-        <v>NA</v>
+        <v>8.5995370370370375E-3</v>
       </c>
       <c r="DI18" s="31"/>
       <c r="DJ18" s="34"/>
       <c r="DK18" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL18" s="35"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM18" s="34">
+        <v>2.7743055555555556E-2</v>
+      </c>
+      <c r="DN18" s="33">
+        <f t="shared" si="27"/>
+        <v>2.3958333333333331E-2</v>
+      </c>
+      <c r="DO18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP18" s="34">
+        <v>6.0648148148148145E-3</v>
+      </c>
+      <c r="DQ18" s="33">
+        <f t="shared" si="28"/>
+        <v>2.2800925925925922E-3</v>
+      </c>
+      <c r="DR18" s="31"/>
+      <c r="DS18" s="34"/>
+      <c r="DT18" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU18" s="31"/>
+      <c r="DV18" s="34"/>
+      <c r="DW18" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX18" s="35"/>
     </row>
-    <row r="19" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>197</v>
       </c>
@@ -6400,7 +6970,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>E4</v>
       </c>
       <c r="G19" s="5">
@@ -6436,7 +7006,7 @@
         <v>4</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.8333333333333293E-2</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -6467,7 +7037,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>6.204861111111111E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -6477,7 +7047,7 @@
         <v>1.5659722222222221E-2</v>
       </c>
       <c r="AF19" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>4.2048611111111113E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -6488,10 +7058,10 @@
       </c>
       <c r="AI19" s="22"/>
       <c r="AJ19" s="29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK19" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL19" s="31">
         <v>2</v>
@@ -6500,7 +7070,7 @@
         <v>4.4675925925925924E-3</v>
       </c>
       <c r="AN19" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>1.2731481481481448E-4</v>
       </c>
       <c r="AO19" s="31">
@@ -6510,7 +7080,7 @@
         <v>3.1550925925925927E-2</v>
       </c>
       <c r="AQ19" s="33">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>2.721064814814815E-2</v>
       </c>
       <c r="AR19" s="31">
@@ -6520,7 +7090,7 @@
         <v>4.417824074074074E-2</v>
       </c>
       <c r="AT19" s="33">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>3.9837962962962964E-2</v>
       </c>
       <c r="AU19" s="31">
@@ -6530,7 +7100,7 @@
         <v>7.2106481481481483E-3</v>
       </c>
       <c r="AW19" s="33">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>2.8703703703703703E-3</v>
       </c>
       <c r="AX19" s="31"/>
@@ -6552,19 +7122,19 @@
         <v>3.9594907407407405E-2</v>
       </c>
       <c r="BF19" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>3.5254629629629629E-2</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31"/>
       <c r="BK19" s="34"/>
       <c r="BL19" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="31">
@@ -6574,25 +7144,25 @@
         <v>1.125E-2</v>
       </c>
       <c r="BO19" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>6.9097222222222216E-3</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="34"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="31"/>
       <c r="BW19" s="32"/>
       <c r="BX19" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BY19" s="31"/>
@@ -6678,12 +7248,44 @@
       <c r="DI19" s="31"/>
       <c r="DJ19" s="34"/>
       <c r="DK19" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL19" s="35"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL19" s="31">
+        <v>2</v>
+      </c>
+      <c r="DM19" s="34">
+        <v>9.7337962962962959E-3</v>
+      </c>
+      <c r="DN19" s="33">
+        <f t="shared" si="27"/>
+        <v>5.393518518518518E-3</v>
+      </c>
+      <c r="DO19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP19" s="34">
+        <v>1.7777777777777778E-2</v>
+      </c>
+      <c r="DQ19" s="33">
+        <f t="shared" si="28"/>
+        <v>1.34375E-2</v>
+      </c>
+      <c r="DR19" s="31"/>
+      <c r="DS19" s="34"/>
+      <c r="DT19" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU19" s="31"/>
+      <c r="DV19" s="34"/>
+      <c r="DW19" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX19" s="35"/>
     </row>
-    <row r="20" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>197</v>
       </c>
@@ -6700,7 +7302,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>E6</v>
       </c>
       <c r="G20" s="5">
@@ -6736,7 +7338,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.6944444444444464E-2</v>
       </c>
       <c r="R20" s="6" t="s">
@@ -6765,7 +7367,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.3761574074074071E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -6773,7 +7375,7 @@
       </c>
       <c r="AE20" s="20"/>
       <c r="AF20" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>3.9039351851851846E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -6792,13 +7394,13 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="34"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31"/>
       <c r="AP20" s="34"/>
       <c r="AQ20" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="31">
@@ -6808,13 +7410,13 @@
         <v>2.78125E-2</v>
       </c>
       <c r="AT20" s="33">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>2.3090277777777779E-2</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -6832,19 +7434,19 @@
       <c r="BD20" s="31"/>
       <c r="BE20" s="34"/>
       <c r="BF20" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31"/>
       <c r="BK20" s="34"/>
       <c r="BL20" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="31">
@@ -6854,19 +7456,19 @@
         <v>3.5439814814814813E-2</v>
       </c>
       <c r="BO20" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>3.0717592592592591E-2</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="31">
@@ -6876,7 +7478,7 @@
         <v>1.2314814814814815E-2</v>
       </c>
       <c r="BX20" s="33">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>7.5925925925925926E-3</v>
       </c>
       <c r="BY20" s="31"/>
@@ -6962,12 +7564,40 @@
       <c r="DI20" s="31"/>
       <c r="DJ20" s="34"/>
       <c r="DK20" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL20" s="35"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL20" s="31"/>
+      <c r="DM20" s="34"/>
+      <c r="DN20" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO20" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP20" s="34">
+        <v>9.2245370370370363E-3</v>
+      </c>
+      <c r="DQ20" s="33">
+        <f t="shared" si="28"/>
+        <v>4.502314814814814E-3</v>
+      </c>
+      <c r="DR20" s="31"/>
+      <c r="DS20" s="34"/>
+      <c r="DT20" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU20" s="31"/>
+      <c r="DV20" s="34"/>
+      <c r="DW20" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX20" s="35"/>
     </row>
-    <row r="21" spans="1:116" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:128" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>197</v>
       </c>
@@ -6984,7 +7614,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="74" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>E5</v>
       </c>
       <c r="G21" s="5">
@@ -7020,7 +7650,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>5.6250000000000022E-2</v>
       </c>
       <c r="R21" s="5" t="s">
@@ -7049,7 +7679,7 @@
       <c r="AA21" s="77"/>
       <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.821759259259259E-2</v>
       </c>
       <c r="AD21" s="78">
@@ -7059,7 +7689,7 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="AF21" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>4.2604166666666665E-2</v>
       </c>
       <c r="AG21" s="21">
@@ -7078,25 +7708,25 @@
       <c r="AL21" s="31"/>
       <c r="AM21" s="32"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31"/>
       <c r="AP21" s="32"/>
       <c r="AQ21" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -7114,19 +7744,19 @@
       <c r="BD21" s="31"/>
       <c r="BE21" s="34"/>
       <c r="BF21" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31"/>
       <c r="BK21" s="32"/>
       <c r="BL21" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM21" s="31">
@@ -7136,25 +7766,25 @@
         <v>1.0254629629629629E-2</v>
       </c>
       <c r="BO21" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>5.9143518518518512E-3</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31"/>
       <c r="BT21" s="32"/>
       <c r="BU21" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV21" s="31"/>
       <c r="BW21" s="32"/>
       <c r="BX21" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BY21" s="31"/>
@@ -7240,19 +7870,51 @@
         <v>3.005787037037037E-2</v>
       </c>
       <c r="DK21" s="33">
-        <f t="shared" si="42"/>
+        <f t="shared" si="26"/>
         <v>2.5717592592592591E-2</v>
       </c>
-      <c r="DL21" s="35"/>
+      <c r="DL21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM21" s="34">
+        <v>2.554398148148148E-2</v>
+      </c>
+      <c r="DN21" s="33">
+        <f t="shared" si="27"/>
+        <v>2.1203703703703704E-2</v>
+      </c>
+      <c r="DO21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP21" s="56">
+        <v>7.7314814814814815E-3</v>
+      </c>
+      <c r="DQ21" s="33">
+        <f t="shared" si="28"/>
+        <v>3.3912037037037036E-3</v>
+      </c>
+      <c r="DR21" s="31"/>
+      <c r="DS21" s="56"/>
+      <c r="DT21" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU21" s="31"/>
+      <c r="DV21" s="56"/>
+      <c r="DW21" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX21" s="35"/>
     </row>
-    <row r="22" spans="1:116" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:128" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="75" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="G22" s="11"/>
@@ -7272,7 +7934,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="12">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="R22" s="11"/>
@@ -7287,13 +7949,13 @@
       <c r="AA22" s="69"/>
       <c r="AB22" s="69"/>
       <c r="AC22" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AD22" s="80"/>
       <c r="AE22" s="80"/>
       <c r="AF22" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AG22" s="24"/>
@@ -7304,25 +7966,25 @@
       <c r="AL22" s="38"/>
       <c r="AM22" s="40"/>
       <c r="AN22" s="41" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
       <c r="AQ22" s="41" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="41" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
       <c r="AV22" s="82"/>
       <c r="AW22" s="41" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
@@ -7340,43 +8002,43 @@
       <c r="BD22" s="38"/>
       <c r="BE22" s="40"/>
       <c r="BF22" s="41" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="38"/>
       <c r="BH22" s="82"/>
       <c r="BI22" s="41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38"/>
       <c r="BK22" s="82"/>
       <c r="BL22" s="41" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BM22" s="38"/>
       <c r="BN22" s="40"/>
       <c r="BO22" s="41" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BP22" s="38"/>
       <c r="BQ22" s="82"/>
       <c r="BR22" s="41" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
       <c r="BT22" s="82"/>
       <c r="BU22" s="41" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="38"/>
       <c r="BW22" s="82"/>
       <c r="BX22" s="41" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BY22" s="38"/>
@@ -7454,10 +8116,34 @@
       <c r="DI22" s="38"/>
       <c r="DJ22" s="40"/>
       <c r="DK22" s="41" t="str">
-        <f t="shared" si="42"/>
-        <v>NA</v>
-      </c>
-      <c r="DL22" s="39"/>
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL22" s="38"/>
+      <c r="DM22" s="40"/>
+      <c r="DN22" s="41" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO22" s="38"/>
+      <c r="DP22" s="40"/>
+      <c r="DQ22" s="41" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR22" s="38"/>
+      <c r="DS22" s="40"/>
+      <c r="DT22" s="41" t="str">
+        <f t="shared" si="29"/>
+        <v>NA</v>
+      </c>
+      <c r="DU22" s="38"/>
+      <c r="DV22" s="40"/>
+      <c r="DW22" s="41" t="str">
+        <f t="shared" si="46"/>
+        <v>NA</v>
+      </c>
+      <c r="DX22" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/URUVS/Datasheets/URUV/08.2024/August_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/08.2024/August_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\08.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3281DAC-00A0-48B1-A1BA-B654F8B7F3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC1D5B3-3CD8-46A1-8735-81253A1BA885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="228">
   <si>
     <t>DATE</t>
   </si>
@@ -714,6 +714,15 @@
   </si>
   <si>
     <t>T1_FISHWTH</t>
+  </si>
+  <si>
+    <t>MAXN_FISHBT</t>
+  </si>
+  <si>
+    <t>TIME_1STFISHBT</t>
+  </si>
+  <si>
+    <t>T1_FISHBT</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DX22"/>
+  <dimension ref="A1:EA22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
@@ -1368,8 +1377,7 @@
     <col min="58" max="58" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -1378,10 +1386,11 @@
     <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="124" max="124" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="127" max="127" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:128" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:131" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>196</v>
       </c>
@@ -1647,127 +1656,136 @@
         <v>209</v>
       </c>
       <c r="CK1" s="81" t="s">
+        <v>225</v>
+      </c>
+      <c r="CL1" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="CM1" s="59" t="s">
+        <v>227</v>
+      </c>
+      <c r="CN1" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="CL1" s="27" t="s">
+      <c r="CO1" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="CM1" s="59" t="s">
+      <c r="CP1" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="CN1" s="81" t="s">
+      <c r="CQ1" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="CO1" s="27" t="s">
+      <c r="CR1" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="CP1" s="59" t="s">
+      <c r="CS1" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="CQ1" s="81" t="s">
+      <c r="CT1" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="CR1" s="27" t="s">
+      <c r="CU1" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="CS1" s="59" t="s">
+      <c r="CV1" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="CT1" s="81" t="s">
+      <c r="CW1" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="CU1" s="27" t="s">
+      <c r="CX1" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="CV1" s="59" t="s">
+      <c r="CY1" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="CW1" s="81" t="s">
+      <c r="CZ1" s="81" t="s">
         <v>210</v>
       </c>
-      <c r="CX1" s="27" t="s">
+      <c r="DA1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="CY1" s="59" t="s">
+      <c r="DB1" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="CZ1" s="81" t="s">
+      <c r="DC1" s="81" t="s">
         <v>141</v>
       </c>
-      <c r="DA1" s="27" t="s">
+      <c r="DD1" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="DB1" s="59" t="s">
+      <c r="DE1" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="DC1" s="81" t="s">
+      <c r="DF1" s="81" t="s">
         <v>204</v>
       </c>
-      <c r="DD1" s="27" t="s">
+      <c r="DG1" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="DE1" s="59" t="s">
+      <c r="DH1" s="59" t="s">
         <v>206</v>
       </c>
-      <c r="DF1" s="81" t="s">
+      <c r="DI1" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="DG1" s="27" t="s">
+      <c r="DJ1" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="DH1" s="59" t="s">
+      <c r="DK1" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="DI1" s="81" t="s">
+      <c r="DL1" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="DJ1" s="27" t="s">
+      <c r="DM1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="DK1" s="59" t="s">
+      <c r="DN1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="DL1" s="81" t="s">
+      <c r="DO1" s="81" t="s">
         <v>213</v>
       </c>
-      <c r="DM1" s="27" t="s">
+      <c r="DP1" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="DN1" s="59" t="s">
+      <c r="DQ1" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="DO1" s="81" t="s">
+      <c r="DR1" s="81" t="s">
         <v>216</v>
       </c>
-      <c r="DP1" s="27" t="s">
+      <c r="DS1" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="DQ1" s="59" t="s">
+      <c r="DT1" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="DR1" s="81" t="s">
+      <c r="DU1" s="81" t="s">
         <v>219</v>
       </c>
-      <c r="DS1" s="27" t="s">
+      <c r="DV1" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="DT1" s="59" t="s">
+      <c r="DW1" s="59" t="s">
         <v>221</v>
       </c>
-      <c r="DU1" s="81" t="s">
+      <c r="DX1" s="81" t="s">
         <v>222</v>
       </c>
-      <c r="DV1" s="27" t="s">
+      <c r="DY1" s="27" t="s">
         <v>223</v>
       </c>
-      <c r="DW1" s="59" t="s">
+      <c r="DZ1" s="59" t="s">
         <v>224</v>
       </c>
-      <c r="DX1" s="28" t="s">
+      <c r="EA1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>197</v>
       </c>
@@ -2009,21 +2027,21 @@
         <f t="shared" ref="CS2:CS22" si="20">IF(CQ2=0,"NA",CR2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CT2" s="58">
+      <c r="CT2" s="58"/>
+      <c r="CU2" s="71"/>
+      <c r="CV2" s="33" t="str">
+        <f t="shared" ref="CV2:CV22" si="21">IF(CT2=0,"NA",CU2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="CW2" s="58">
         <v>1</v>
       </c>
-      <c r="CU2" s="71">
+      <c r="CX2" s="71">
         <v>1.7592592592592594E-2</v>
       </c>
-      <c r="CV2" s="33">
-        <f t="shared" ref="CV2:CV22" si="21">IF(CT2=0,"NA",CU2-$AD2)</f>
+      <c r="CY2" s="33">
+        <f t="shared" ref="CY2:CY22" si="22">IF(CW2=0,"NA",CX2-$AD2)</f>
         <v>1.4120370370370372E-2</v>
-      </c>
-      <c r="CW2" s="58"/>
-      <c r="CX2" s="71"/>
-      <c r="CY2" s="33" t="str">
-        <f t="shared" ref="CY2:CY22" si="22">IF(CW2=0,"NA",CX2-$AD2)</f>
-        <v>NA</v>
       </c>
       <c r="CZ2" s="58"/>
       <c r="DA2" s="71"/>
@@ -2037,21 +2055,21 @@
         <f t="shared" ref="DE2:DE22" si="24">IF(DC2=0,"NA",DD2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="DF2" s="58">
+      <c r="DF2" s="58"/>
+      <c r="DG2" s="71"/>
+      <c r="DH2" s="33" t="str">
+        <f t="shared" ref="DH2:DH22" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DI2" s="58">
         <v>1</v>
       </c>
-      <c r="DG2" s="71">
+      <c r="DJ2" s="71">
         <v>2.0532407407407409E-2</v>
       </c>
-      <c r="DH2" s="33">
-        <f t="shared" ref="DH2:DH22" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+      <c r="DK2" s="33">
+        <f t="shared" ref="DK2:DK22" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
         <v>1.7060185185185185E-2</v>
-      </c>
-      <c r="DI2" s="58"/>
-      <c r="DJ2" s="71"/>
-      <c r="DK2" s="33" t="str">
-        <f t="shared" ref="DK2:DK22" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
-        <v>NA</v>
       </c>
       <c r="DL2" s="58"/>
       <c r="DM2" s="71"/>
@@ -2059,31 +2077,37 @@
         <f t="shared" ref="DN2:DN22" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="DO2" s="58">
+      <c r="DO2" s="58"/>
+      <c r="DP2" s="71"/>
+      <c r="DQ2" s="33" t="str">
+        <f t="shared" ref="DQ2:DQ22" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DR2" s="58">
         <v>1</v>
       </c>
-      <c r="DP2" s="71">
+      <c r="DS2" s="71">
         <v>3.1087962962962963E-2</v>
       </c>
-      <c r="DQ2" s="33">
-        <f t="shared" ref="DQ2:DQ22" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
+      <c r="DT2" s="33">
+        <f t="shared" ref="DT2:DT22" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
         <v>2.7615740740740739E-2</v>
-      </c>
-      <c r="DR2" s="58"/>
-      <c r="DS2" s="71"/>
-      <c r="DT2" s="33" t="str">
-        <f t="shared" ref="DT2:DT22" si="29">IF(DR2=0,"NA",DS2-$AD2)</f>
-        <v>NA</v>
       </c>
       <c r="DU2" s="58"/>
       <c r="DV2" s="71"/>
       <c r="DW2" s="33" t="str">
-        <f t="shared" ref="DW2:DW13" si="30">IF(DU2=0,"NA",DV2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="DX2" s="35"/>
+        <f t="shared" ref="DW2:DW22" si="30">IF(DU2=0,"NA",DV2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DX2" s="58"/>
+      <c r="DY2" s="71"/>
+      <c r="DZ2" s="33" t="str">
+        <f t="shared" ref="DZ2:DZ13" si="31">IF(DX2=0,"NA",DY2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="EA2" s="35"/>
     </row>
-    <row r="3" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>197</v>
       </c>
@@ -2100,7 +2124,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F22" si="31">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F22" si="32">D3&amp;""&amp;E3</f>
         <v>E3</v>
       </c>
       <c r="G3" s="5">
@@ -2136,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q22" si="32">J3-I3</f>
+        <f t="shared" ref="Q3:Q22" si="33">J3-I3</f>
         <v>7.6388888888888895E-2</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2167,7 +2191,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="33">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="34">SUM(W3:AB3)</f>
         <v>4.1805555555555554E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2295,21 +2319,21 @@
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
-      <c r="CH3" s="31">
+      <c r="CH3" s="31"/>
+      <c r="CI3" s="34"/>
+      <c r="CJ3" s="33" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CK3" s="31">
         <v>1</v>
       </c>
-      <c r="CI3" s="34">
+      <c r="CL3" s="34">
         <v>3.667824074074074E-2</v>
       </c>
-      <c r="CJ3" s="33">
-        <f t="shared" si="17"/>
+      <c r="CM3" s="33">
+        <f t="shared" si="18"/>
         <v>3.3206018518518517E-2</v>
-      </c>
-      <c r="CK3" s="31"/>
-      <c r="CL3" s="32"/>
-      <c r="CM3" s="33" t="str">
-        <f t="shared" si="18"/>
-        <v>NA</v>
       </c>
       <c r="CN3" s="31"/>
       <c r="CO3" s="32"/>
@@ -2347,21 +2371,21 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF3" s="31">
+      <c r="DF3" s="31"/>
+      <c r="DG3" s="32"/>
+      <c r="DH3" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI3" s="31">
         <v>1</v>
       </c>
-      <c r="DG3" s="34">
+      <c r="DJ3" s="34">
         <v>2.5324074074074075E-2</v>
       </c>
-      <c r="DH3" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK3" s="33">
+        <f t="shared" si="26"/>
         <v>2.1851851851851851E-2</v>
-      </c>
-      <c r="DI3" s="31"/>
-      <c r="DJ3" s="32"/>
-      <c r="DK3" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
       </c>
       <c r="DL3" s="31"/>
       <c r="DM3" s="32"/>
@@ -2369,21 +2393,21 @@
         <f t="shared" si="27"/>
         <v>NA</v>
       </c>
-      <c r="DO3" s="31">
+      <c r="DO3" s="31"/>
+      <c r="DP3" s="32"/>
+      <c r="DQ3" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR3" s="31">
         <v>1</v>
       </c>
-      <c r="DP3" s="34">
+      <c r="DS3" s="34">
         <v>2.6064814814814815E-2</v>
       </c>
-      <c r="DQ3" s="33">
-        <f t="shared" si="28"/>
+      <c r="DT3" s="33">
+        <f t="shared" si="29"/>
         <v>2.2592592592592595E-2</v>
-      </c>
-      <c r="DR3" s="31"/>
-      <c r="DS3" s="32"/>
-      <c r="DT3" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU3" s="31"/>
       <c r="DV3" s="32"/>
@@ -2391,9 +2415,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX3" s="35"/>
+      <c r="DX3" s="31"/>
+      <c r="DY3" s="32"/>
+      <c r="DZ3" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA3" s="35"/>
     </row>
-    <row r="4" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>197</v>
       </c>
@@ -2410,7 +2440,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>E1</v>
       </c>
       <c r="G4" s="5">
@@ -2446,7 +2476,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.3611111111111127E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2475,7 +2505,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5.6145833333333339E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2631,21 +2661,21 @@
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW4" s="31">
+      <c r="CW4" s="31"/>
+      <c r="CX4" s="34"/>
+      <c r="CY4" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ4" s="31">
         <v>1</v>
       </c>
-      <c r="CX4" s="34">
+      <c r="DA4" s="34">
         <v>2.2037037037037036E-2</v>
       </c>
-      <c r="CY4" s="33">
-        <f t="shared" si="22"/>
+      <c r="DB4" s="33">
+        <f t="shared" si="23"/>
         <v>1.1620370370370369E-2</v>
-      </c>
-      <c r="CZ4" s="31"/>
-      <c r="DA4" s="34"/>
-      <c r="DB4" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v>NA</v>
       </c>
       <c r="DC4" s="31"/>
       <c r="DD4" s="34"/>
@@ -2689,9 +2719,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX4" s="35"/>
+      <c r="DX4" s="31"/>
+      <c r="DY4" s="34"/>
+      <c r="DZ4" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA4" s="35"/>
     </row>
-    <row r="5" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>197</v>
       </c>
@@ -2708,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D2</v>
       </c>
       <c r="G5" s="5">
@@ -2744,7 +2780,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.2916666666666685E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2773,7 +2809,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2.8333333333333332E-2</v>
       </c>
       <c r="AD5" s="20">
@@ -2911,21 +2947,21 @@
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK5" s="31">
+      <c r="CK5" s="31"/>
+      <c r="CL5" s="32"/>
+      <c r="CM5" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN5" s="31">
         <v>1</v>
       </c>
-      <c r="CL5" s="34">
+      <c r="CO5" s="34">
         <v>4.4560185185185189E-3</v>
       </c>
-      <c r="CM5" s="33">
-        <f t="shared" si="18"/>
+      <c r="CP5" s="33">
+        <f t="shared" si="19"/>
         <v>3.9351851851851874E-4</v>
-      </c>
-      <c r="CN5" s="31"/>
-      <c r="CO5" s="32"/>
-      <c r="CP5" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
       </c>
       <c r="CQ5" s="31"/>
       <c r="CR5" s="32"/>
@@ -2957,21 +2993,21 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF5" s="31">
+      <c r="DF5" s="31"/>
+      <c r="DG5" s="32"/>
+      <c r="DH5" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI5" s="31">
         <v>1</v>
       </c>
-      <c r="DG5" s="34">
+      <c r="DJ5" s="34">
         <v>2.1689814814814815E-2</v>
       </c>
-      <c r="DH5" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK5" s="33">
+        <f t="shared" si="26"/>
         <v>1.7627314814814814E-2</v>
-      </c>
-      <c r="DI5" s="31"/>
-      <c r="DJ5" s="32"/>
-      <c r="DK5" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
       </c>
       <c r="DL5" s="31"/>
       <c r="DM5" s="32"/>
@@ -2979,35 +3015,41 @@
         <f t="shared" si="27"/>
         <v>NA</v>
       </c>
-      <c r="DO5" s="31">
+      <c r="DO5" s="31"/>
+      <c r="DP5" s="32"/>
+      <c r="DQ5" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR5" s="31">
         <v>1</v>
       </c>
-      <c r="DP5" s="34">
+      <c r="DS5" s="34">
         <v>2.3229166666666665E-2</v>
       </c>
-      <c r="DQ5" s="33">
-        <f t="shared" si="28"/>
+      <c r="DT5" s="33">
+        <f t="shared" si="29"/>
         <v>1.9166666666666665E-2</v>
       </c>
-      <c r="DR5" s="31"/>
-      <c r="DS5" s="32"/>
-      <c r="DT5" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
-      </c>
-      <c r="DU5" s="31">
+      <c r="DU5" s="31"/>
+      <c r="DV5" s="32"/>
+      <c r="DW5" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX5" s="31">
         <v>1</v>
       </c>
-      <c r="DV5" s="34">
+      <c r="DY5" s="34">
         <v>5.6134259259259262E-3</v>
       </c>
-      <c r="DW5" s="33">
-        <f t="shared" si="30"/>
+      <c r="DZ5" s="33">
+        <f t="shared" si="31"/>
         <v>1.5509259259259261E-3</v>
       </c>
-      <c r="DX5" s="35"/>
+      <c r="EA5" s="35"/>
     </row>
-    <row r="6" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>197</v>
       </c>
@@ -3024,7 +3066,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D3</v>
       </c>
       <c r="G6" s="5">
@@ -3060,7 +3102,7 @@
         <v>6</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.0833333333333304E-2</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -3095,7 +3137,7 @@
         <v>1.5277777777777779E-3</v>
       </c>
       <c r="AC6" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>7.6736111111111102E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -3240,7 +3282,7 @@
         <v>1.1145833333333334E-2</v>
       </c>
       <c r="CK6" s="31"/>
-      <c r="CL6" s="32"/>
+      <c r="CL6" s="34"/>
       <c r="CM6" s="33" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
@@ -3293,31 +3335,31 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL6" s="31">
-        <v>1</v>
-      </c>
-      <c r="DM6" s="34">
-        <v>3.4155092592592591E-2</v>
-      </c>
-      <c r="DN6" s="33">
+      <c r="DL6" s="31"/>
+      <c r="DM6" s="32"/>
+      <c r="DN6" s="33" t="str">
         <f t="shared" si="27"/>
-        <v>2.9826388888888888E-2</v>
+        <v>NA</v>
       </c>
       <c r="DO6" s="31">
         <v>1</v>
       </c>
       <c r="DP6" s="34">
-        <v>3.0682870370370371E-2</v>
+        <v>3.4155092592592591E-2</v>
       </c>
       <c r="DQ6" s="33">
         <f t="shared" si="28"/>
+        <v>2.9826388888888888E-2</v>
+      </c>
+      <c r="DR6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS6" s="34">
+        <v>3.0682870370370371E-2</v>
+      </c>
+      <c r="DT6" s="33">
+        <f t="shared" si="29"/>
         <v>2.6354166666666668E-2</v>
-      </c>
-      <c r="DR6" s="31"/>
-      <c r="DS6" s="32"/>
-      <c r="DT6" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU6" s="31"/>
       <c r="DV6" s="32"/>
@@ -3325,9 +3367,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX6" s="35"/>
+      <c r="DX6" s="31"/>
+      <c r="DY6" s="32"/>
+      <c r="DZ6" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA6" s="35"/>
     </row>
-    <row r="7" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>197</v>
       </c>
@@ -3344,7 +3392,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L2</v>
       </c>
       <c r="G7" s="5">
@@ -3380,7 +3428,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.9166666666666663E-2</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -3409,7 +3457,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5.631944444444445E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3587,41 +3635,41 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF7" s="31">
+      <c r="DF7" s="31"/>
+      <c r="DG7" s="32"/>
+      <c r="DH7" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI7" s="31">
         <v>1</v>
       </c>
-      <c r="DG7" s="34">
+      <c r="DJ7" s="34">
         <v>2.0648148148148148E-2</v>
-      </c>
-      <c r="DH7" s="33">
-        <f t="shared" si="25"/>
-        <v>1.5949074074074074E-2</v>
-      </c>
-      <c r="DI7" s="31">
-        <v>3</v>
-      </c>
-      <c r="DJ7" s="34">
-        <v>1.1331018518518518E-2</v>
       </c>
       <c r="DK7" s="33">
         <f t="shared" si="26"/>
-        <v>6.6319444444444438E-3</v>
+        <v>1.5949074074074074E-2</v>
       </c>
       <c r="DL7" s="31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DM7" s="34">
-        <v>3.3703703703703701E-2</v>
+        <v>1.1331018518518518E-2</v>
       </c>
       <c r="DN7" s="33">
         <f t="shared" si="27"/>
+        <v>6.6319444444444438E-3</v>
+      </c>
+      <c r="DO7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP7" s="34">
+        <v>3.3703703703703701E-2</v>
+      </c>
+      <c r="DQ7" s="33">
+        <f t="shared" si="28"/>
         <v>2.9004629629629627E-2</v>
-      </c>
-      <c r="DO7" s="31"/>
-      <c r="DP7" s="34"/>
-      <c r="DQ7" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR7" s="31"/>
       <c r="DS7" s="34"/>
@@ -3635,9 +3683,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX7" s="35"/>
+      <c r="DX7" s="31"/>
+      <c r="DY7" s="34"/>
+      <c r="DZ7" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA7" s="35"/>
     </row>
-    <row r="8" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>197</v>
       </c>
@@ -3654,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L1</v>
       </c>
       <c r="G8" s="5">
@@ -3690,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -3719,7 +3773,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.0960648148148153E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3880,7 +3934,7 @@
         <v>NA</v>
       </c>
       <c r="CW8" s="31"/>
-      <c r="CX8" s="70"/>
+      <c r="CX8" s="32"/>
       <c r="CY8" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
@@ -3903,51 +3957,57 @@
         <f t="shared" si="25"/>
         <v>NA</v>
       </c>
-      <c r="DI8" s="31">
+      <c r="DI8" s="31"/>
+      <c r="DJ8" s="70"/>
+      <c r="DK8" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL8" s="31">
         <v>2</v>
       </c>
-      <c r="DJ8" s="70">
+      <c r="DM8" s="70">
         <v>2.1030092592592593E-2</v>
       </c>
-      <c r="DK8" s="33">
-        <f t="shared" si="26"/>
+      <c r="DN8" s="33">
+        <f t="shared" si="27"/>
         <v>1.6250000000000001E-2</v>
       </c>
-      <c r="DL8" s="31"/>
-      <c r="DM8" s="70"/>
-      <c r="DN8" s="33" t="str">
-        <f t="shared" si="27"/>
-        <v>NA</v>
-      </c>
-      <c r="DO8" s="31">
-        <v>1</v>
-      </c>
-      <c r="DP8" s="70">
-        <v>3.0497685185185187E-2</v>
-      </c>
-      <c r="DQ8" s="33">
+      <c r="DO8" s="31"/>
+      <c r="DP8" s="70"/>
+      <c r="DQ8" s="33" t="str">
         <f t="shared" si="28"/>
-        <v>2.5717592592592594E-2</v>
+        <v>NA</v>
       </c>
       <c r="DR8" s="31">
         <v>1</v>
       </c>
       <c r="DS8" s="70">
-        <v>2.2175925925925925E-2</v>
+        <v>3.0497685185185187E-2</v>
       </c>
       <c r="DT8" s="33">
         <f t="shared" si="29"/>
+        <v>2.5717592592592594E-2</v>
+      </c>
+      <c r="DU8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DV8" s="70">
+        <v>2.2175925925925925E-2</v>
+      </c>
+      <c r="DW8" s="33">
+        <f t="shared" si="30"/>
         <v>1.7395833333333333E-2</v>
       </c>
-      <c r="DU8" s="31"/>
-      <c r="DV8" s="70"/>
-      <c r="DW8" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v>NA</v>
-      </c>
-      <c r="DX8" s="35"/>
+      <c r="DX8" s="31"/>
+      <c r="DY8" s="70"/>
+      <c r="DZ8" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA8" s="35"/>
     </row>
-    <row r="9" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>197</v>
       </c>
@@ -3964,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L3</v>
       </c>
       <c r="G9" s="5">
@@ -4000,7 +4060,7 @@
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.8333333333333293E-2</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -4029,7 +4089,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5.9305555555555556E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -4190,7 +4250,7 @@
         <v>NA</v>
       </c>
       <c r="CW9" s="31"/>
-      <c r="CX9" s="56"/>
+      <c r="CX9" s="32"/>
       <c r="CY9" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
@@ -4207,31 +4267,31 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF9" s="31">
+      <c r="DF9" s="31"/>
+      <c r="DG9" s="56"/>
+      <c r="DH9" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI9" s="31">
         <v>1</v>
       </c>
-      <c r="DG9" s="56">
+      <c r="DJ9" s="56">
         <v>2.8668981481481483E-2</v>
-      </c>
-      <c r="DH9" s="33">
-        <f t="shared" si="25"/>
-        <v>2.4050925925925927E-2</v>
-      </c>
-      <c r="DI9" s="31">
-        <v>3</v>
-      </c>
-      <c r="DJ9" s="56">
-        <v>5.2777777777777779E-3</v>
       </c>
       <c r="DK9" s="33">
         <f t="shared" si="26"/>
+        <v>2.4050925925925927E-2</v>
+      </c>
+      <c r="DL9" s="31">
+        <v>3</v>
+      </c>
+      <c r="DM9" s="56">
+        <v>5.2777777777777779E-3</v>
+      </c>
+      <c r="DN9" s="33">
+        <f t="shared" si="27"/>
         <v>6.5972222222222213E-4</v>
-      </c>
-      <c r="DL9" s="31"/>
-      <c r="DM9" s="56"/>
-      <c r="DN9" s="33" t="str">
-        <f t="shared" si="27"/>
-        <v>NA</v>
       </c>
       <c r="DO9" s="31"/>
       <c r="DP9" s="56"/>
@@ -4251,9 +4311,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX9" s="35"/>
+      <c r="DX9" s="31"/>
+      <c r="DY9" s="56"/>
+      <c r="DZ9" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA9" s="35"/>
     </row>
-    <row r="10" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>197</v>
       </c>
@@ -4270,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D1</v>
       </c>
       <c r="G10" s="5">
@@ -4306,7 +4372,7 @@
         <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.6944444444444409E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -4335,7 +4401,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.1331018518518517E-2</v>
       </c>
       <c r="AD10" s="20">
@@ -4523,21 +4589,21 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL10" s="31">
+      <c r="DL10" s="31"/>
+      <c r="DM10" s="34"/>
+      <c r="DN10" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO10" s="31">
         <v>1</v>
       </c>
-      <c r="DM10" s="34">
+      <c r="DP10" s="34">
         <v>2.6620370370370371E-2</v>
       </c>
-      <c r="DN10" s="33">
-        <f t="shared" si="27"/>
+      <c r="DQ10" s="33">
+        <f t="shared" si="28"/>
         <v>2.2106481481481484E-2</v>
-      </c>
-      <c r="DO10" s="31"/>
-      <c r="DP10" s="34"/>
-      <c r="DQ10" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR10" s="31"/>
       <c r="DS10" s="34"/>
@@ -4551,9 +4617,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX10" s="35"/>
+      <c r="DX10" s="31"/>
+      <c r="DY10" s="34"/>
+      <c r="DZ10" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA10" s="35"/>
     </row>
-    <row r="11" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>197</v>
       </c>
@@ -4570,7 +4642,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D4</v>
       </c>
       <c r="G11" s="5">
@@ -4606,7 +4678,7 @@
         <v>5</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.6111111111111083E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -4639,7 +4711,7 @@
       </c>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>7.0300925925925919E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4813,21 +4885,21 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF11" s="31">
+      <c r="DF11" s="31"/>
+      <c r="DG11" s="34"/>
+      <c r="DH11" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI11" s="31">
         <v>1</v>
       </c>
-      <c r="DG11" s="34">
+      <c r="DJ11" s="34">
         <v>2.5601851851851851E-2</v>
       </c>
-      <c r="DH11" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK11" s="33">
+        <f t="shared" si="26"/>
         <v>2.1423611111111109E-2</v>
-      </c>
-      <c r="DI11" s="31"/>
-      <c r="DJ11" s="34"/>
-      <c r="DK11" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
       </c>
       <c r="DL11" s="31"/>
       <c r="DM11" s="34"/>
@@ -4835,35 +4907,41 @@
         <f t="shared" si="27"/>
         <v>NA</v>
       </c>
-      <c r="DO11" s="31">
-        <v>1</v>
-      </c>
-      <c r="DP11" s="34">
-        <v>2.1342592592592594E-2</v>
-      </c>
-      <c r="DQ11" s="33">
+      <c r="DO11" s="31"/>
+      <c r="DP11" s="34"/>
+      <c r="DQ11" s="33" t="str">
         <f t="shared" si="28"/>
-        <v>1.7164351851851854E-2</v>
+        <v>NA</v>
       </c>
       <c r="DR11" s="31">
         <v>1</v>
       </c>
       <c r="DS11" s="34">
-        <v>4.0972222222222222E-2</v>
+        <v>2.1342592592592594E-2</v>
       </c>
       <c r="DT11" s="33">
         <f t="shared" si="29"/>
+        <v>1.7164351851851854E-2</v>
+      </c>
+      <c r="DU11" s="31">
+        <v>1</v>
+      </c>
+      <c r="DV11" s="34">
+        <v>4.0972222222222222E-2</v>
+      </c>
+      <c r="DW11" s="33">
+        <f t="shared" si="30"/>
         <v>3.6793981481481483E-2</v>
       </c>
-      <c r="DU11" s="31"/>
-      <c r="DV11" s="34"/>
-      <c r="DW11" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v>NA</v>
-      </c>
-      <c r="DX11" s="35"/>
+      <c r="DX11" s="31"/>
+      <c r="DY11" s="34"/>
+      <c r="DZ11" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA11" s="35"/>
     </row>
-    <row r="12" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>197</v>
       </c>
@@ -4880,7 +4958,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L6</v>
       </c>
       <c r="G12" s="5">
@@ -4916,7 +4994,7 @@
         <v>4</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.4722222222222199E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -4947,7 +5025,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.9004629629629638E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -5145,21 +5223,21 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL12" s="31">
+      <c r="DL12" s="31"/>
+      <c r="DM12" s="70"/>
+      <c r="DN12" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO12" s="31">
         <v>1</v>
       </c>
-      <c r="DM12" s="70">
+      <c r="DP12" s="70">
         <v>2.3379629629629629E-2</v>
       </c>
-      <c r="DN12" s="33">
-        <f t="shared" si="27"/>
+      <c r="DQ12" s="33">
+        <f t="shared" si="28"/>
         <v>1.9189814814814812E-2</v>
-      </c>
-      <c r="DO12" s="31"/>
-      <c r="DP12" s="70"/>
-      <c r="DQ12" s="33" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
       </c>
       <c r="DR12" s="31"/>
       <c r="DS12" s="70"/>
@@ -5173,9 +5251,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX12" s="35"/>
+      <c r="DX12" s="31"/>
+      <c r="DY12" s="70"/>
+      <c r="DZ12" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA12" s="35"/>
     </row>
-    <row r="13" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>197</v>
       </c>
@@ -5192,7 +5276,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D5</v>
       </c>
       <c r="G13" s="5">
@@ -5228,7 +5312,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.2916666666666685E-2</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -5253,7 +5337,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AD13" s="20"/>
@@ -5382,7 +5466,7 @@
         <v>NA</v>
       </c>
       <c r="CQ13" s="31"/>
-      <c r="CR13" s="34"/>
+      <c r="CR13" s="32"/>
       <c r="CS13" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
@@ -5394,7 +5478,7 @@
         <v>NA</v>
       </c>
       <c r="CW13" s="31"/>
-      <c r="CX13" s="32"/>
+      <c r="CX13" s="34"/>
       <c r="CY13" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
@@ -5447,9 +5531,15 @@
         <f t="shared" si="30"/>
         <v>NA</v>
       </c>
-      <c r="DX13" s="35"/>
+      <c r="DX13" s="31"/>
+      <c r="DY13" s="32"/>
+      <c r="DZ13" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="EA13" s="35"/>
     </row>
-    <row r="14" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>197</v>
       </c>
@@ -5466,7 +5556,7 @@
         <v>5</v>
       </c>
       <c r="F14" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L5</v>
       </c>
       <c r="G14" s="5">
@@ -5502,7 +5592,7 @@
         <v>3</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.0833333333333304E-2</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -5531,7 +5621,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>5.0659722222222217E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -5541,7 +5631,7 @@
         <v>3.9814814814814817E-3</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="34">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="35">AC14-AD14-AE14</f>
         <v>4.1932870370370363E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -5560,25 +5650,25 @@
       <c r="AL14" s="31"/>
       <c r="AM14" s="32"/>
       <c r="AN14" s="33" t="str">
-        <f t="shared" ref="AN14:AN22" si="35">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="36">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="36">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="37">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT22" si="37">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="38">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW22" si="38">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="39">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5600,43 +5690,43 @@
         <v>2.8958333333333332E-2</v>
       </c>
       <c r="BF14" s="33">
-        <f t="shared" ref="BF14:BF22" si="39">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF22" si="40">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>2.4212962962962964E-2</v>
       </c>
       <c r="BG14" s="31"/>
       <c r="BH14" s="32"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI22" si="40">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="41">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="34"/>
       <c r="BL14" s="33" t="str">
-        <f t="shared" ref="BL14:BL22" si="41">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="42">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BM14" s="31"/>
       <c r="BN14" s="34"/>
       <c r="BO14" s="33" t="str">
-        <f t="shared" ref="BO14:BO22" si="42">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="43">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR22" si="43">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="44">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="32"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU22" si="44">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU22" si="45">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BV14" s="31"/>
       <c r="BW14" s="34"/>
       <c r="BX14" s="33" t="str">
-        <f t="shared" ref="BX14:BX22" si="45">IF(BV14=0,"NA",BW14-$AD14)</f>
+        <f t="shared" ref="BX14:BX22" si="46">IF(BV14=0,"NA",BW14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BY14" s="31"/>
@@ -5699,71 +5789,77 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC14" s="31">
-        <v>1</v>
-      </c>
-      <c r="DD14" s="34">
-        <v>3.9733796296296295E-2</v>
-      </c>
-      <c r="DE14" s="33">
+      <c r="DC14" s="31"/>
+      <c r="DD14" s="32"/>
+      <c r="DE14" s="33" t="str">
         <f t="shared" si="24"/>
-        <v>3.4988425925925923E-2</v>
+        <v>NA</v>
       </c>
       <c r="DF14" s="31">
         <v>1</v>
       </c>
       <c r="DG14" s="34">
-        <v>1.0810185185185185E-2</v>
+        <v>3.9733796296296295E-2</v>
       </c>
       <c r="DH14" s="33">
         <f t="shared" si="25"/>
-        <v>6.0648148148148145E-3</v>
+        <v>3.4988425925925923E-2</v>
       </c>
       <c r="DI14" s="31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DJ14" s="34">
-        <v>3.3321759259259259E-2</v>
+        <v>1.0810185185185185E-2</v>
       </c>
       <c r="DK14" s="33">
         <f t="shared" si="26"/>
-        <v>2.8576388888888887E-2</v>
+        <v>6.0648148148148145E-3</v>
       </c>
       <c r="DL14" s="31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="DM14" s="34">
-        <v>1.6446759259259258E-2</v>
+        <v>3.3321759259259259E-2</v>
       </c>
       <c r="DN14" s="33">
         <f t="shared" si="27"/>
-        <v>1.1701388888888888E-2</v>
+        <v>2.8576388888888887E-2</v>
       </c>
       <c r="DO14" s="31">
         <v>1</v>
       </c>
       <c r="DP14" s="34">
-        <v>5.6712962962962967E-3</v>
+        <v>1.6446759259259258E-2</v>
       </c>
       <c r="DQ14" s="33">
         <f t="shared" si="28"/>
+        <v>1.1701388888888888E-2</v>
+      </c>
+      <c r="DR14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS14" s="34">
+        <v>5.6712962962962967E-3</v>
+      </c>
+      <c r="DT14" s="33">
+        <f t="shared" si="29"/>
         <v>9.2592592592592639E-4</v>
-      </c>
-      <c r="DR14" s="31"/>
-      <c r="DS14" s="34"/>
-      <c r="DT14" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU14" s="31"/>
       <c r="DV14" s="34"/>
       <c r="DW14" s="33" t="str">
-        <f t="shared" ref="DW14:DW22" si="46">IF(DU14=0,"NA",DV14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="DX14" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX14" s="31"/>
+      <c r="DY14" s="34"/>
+      <c r="DZ14" s="33" t="str">
+        <f t="shared" ref="DZ14:DZ22" si="47">IF(DX14=0,"NA",DY14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="EA14" s="35"/>
     </row>
-    <row r="15" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>197</v>
       </c>
@@ -5780,7 +5876,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L4</v>
       </c>
       <c r="G15" s="5">
@@ -5816,7 +5912,7 @@
         <v>4</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.8333333333333348E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -5841,13 +5937,13 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AD15" s="20"/>
       <c r="AE15" s="20"/>
       <c r="AF15" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG15" s="21"/>
@@ -5858,25 +5954,25 @@
       <c r="AL15" s="31"/>
       <c r="AM15" s="34"/>
       <c r="AN15" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO15" s="31"/>
       <c r="AP15" s="32"/>
       <c r="AQ15" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5894,43 +5990,43 @@
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
       <c r="BH15" s="32"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31"/>
       <c r="BK15" s="34"/>
       <c r="BL15" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="31"/>
       <c r="BN15" s="32"/>
       <c r="BO15" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="32"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV15" s="31"/>
       <c r="BW15" s="34"/>
       <c r="BX15" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BY15" s="31"/>
@@ -5964,7 +6060,7 @@
         <v>NA</v>
       </c>
       <c r="CN15" s="31"/>
-      <c r="CO15" s="32"/>
+      <c r="CO15" s="70"/>
       <c r="CP15" s="33" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
@@ -6032,12 +6128,18 @@
       <c r="DU15" s="31"/>
       <c r="DV15" s="32"/>
       <c r="DW15" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX15" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX15" s="31"/>
+      <c r="DY15" s="32"/>
+      <c r="DZ15" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA15" s="35"/>
     </row>
-    <row r="16" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>197</v>
       </c>
@@ -6054,7 +6156,7 @@
         <v>6</v>
       </c>
       <c r="F16" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D6</v>
       </c>
       <c r="G16" s="5">
@@ -6090,7 +6192,7 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.7638888888888906E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -6119,7 +6221,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3.9571759259259258E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -6127,7 +6229,7 @@
       </c>
       <c r="AE16" s="20"/>
       <c r="AF16" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.5243055555555555E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -6146,25 +6248,25 @@
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -6182,43 +6284,43 @@
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
       <c r="BI16" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
       <c r="BL16" s="56" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM16" s="31"/>
       <c r="BN16" s="34"/>
       <c r="BO16" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31"/>
       <c r="BT16" s="32"/>
       <c r="BU16" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV16" s="31"/>
       <c r="BW16" s="56"/>
       <c r="BX16" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BY16" s="31"/>
@@ -6305,31 +6407,37 @@
         <f t="shared" si="27"/>
         <v>NA</v>
       </c>
-      <c r="DO16" s="31">
+      <c r="DO16" s="31"/>
+      <c r="DP16" s="34"/>
+      <c r="DQ16" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR16" s="31">
         <v>1</v>
       </c>
-      <c r="DP16" s="34">
+      <c r="DS16" s="34">
         <v>6.5856481481481478E-3</v>
       </c>
-      <c r="DQ16" s="33">
-        <f t="shared" si="28"/>
+      <c r="DT16" s="33">
+        <f t="shared" si="29"/>
         <v>2.2569444444444442E-3</v>
-      </c>
-      <c r="DR16" s="31"/>
-      <c r="DS16" s="34"/>
-      <c r="DT16" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU16" s="31"/>
       <c r="DV16" s="34"/>
       <c r="DW16" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX16" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX16" s="31"/>
+      <c r="DY16" s="34"/>
+      <c r="DZ16" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA16" s="35"/>
     </row>
-    <row r="17" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>197</v>
       </c>
@@ -6346,7 +6454,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>D5</v>
       </c>
       <c r="G17" s="5">
@@ -6382,7 +6490,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -6413,7 +6521,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.1377314814814811E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -6421,7 +6529,7 @@
       </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.6238425925925924E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -6440,25 +6548,25 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -6480,37 +6588,37 @@
         <v>1.0462962962962962E-2</v>
       </c>
       <c r="BF17" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>5.3240740740740731E-3</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31"/>
       <c r="BK17" s="34"/>
       <c r="BL17" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31"/>
       <c r="BT17" s="34"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="31">
@@ -6520,7 +6628,7 @@
         <v>6.7592592592592591E-3</v>
       </c>
       <c r="BX17" s="33">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.6203703703703701E-3</v>
       </c>
       <c r="BY17" s="31"/>
@@ -6601,41 +6709,47 @@
         <f t="shared" si="26"/>
         <v>NA</v>
       </c>
-      <c r="DL17" s="31">
+      <c r="DL17" s="31"/>
+      <c r="DM17" s="34"/>
+      <c r="DN17" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO17" s="31">
         <v>3</v>
       </c>
-      <c r="DM17" s="34">
+      <c r="DP17" s="34">
         <v>5.138888888888889E-3</v>
-      </c>
-      <c r="DN17" s="33">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="DO17" s="31">
-        <v>2</v>
-      </c>
-      <c r="DP17" s="34">
-        <v>6.2500000000000003E-3</v>
       </c>
       <c r="DQ17" s="33">
         <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="DR17" s="31">
+        <v>2</v>
+      </c>
+      <c r="DS17" s="34">
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="DT17" s="33">
+        <f t="shared" si="29"/>
         <v>1.1111111111111113E-3</v>
-      </c>
-      <c r="DR17" s="31"/>
-      <c r="DS17" s="34"/>
-      <c r="DT17" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU17" s="31"/>
       <c r="DV17" s="34"/>
       <c r="DW17" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX17" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX17" s="31"/>
+      <c r="DY17" s="34"/>
+      <c r="DZ17" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA17" s="35"/>
     </row>
-    <row r="18" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>197</v>
       </c>
@@ -6652,7 +6766,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>L4</v>
       </c>
       <c r="G18" s="5">
@@ -6688,7 +6802,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.9305555555555536E-2</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -6719,7 +6833,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.2268518518518518E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6727,7 +6841,7 @@
       </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.8483796296296294E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6746,7 +6860,7 @@
       <c r="AL18" s="31"/>
       <c r="AM18" s="34"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="87">
@@ -6756,19 +6870,19 @@
         <v>6.4004629629629628E-3</v>
       </c>
       <c r="AQ18" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.6157407407407405E-3</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -6794,19 +6908,19 @@
         <v>1.3020833333333334E-2</v>
       </c>
       <c r="BF18" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>9.2361111111111116E-3</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31"/>
       <c r="BK18" s="34"/>
       <c r="BL18" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="31">
@@ -6816,25 +6930,25 @@
         <v>4.6412037037037038E-3</v>
       </c>
       <c r="BO18" s="33">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>8.564814814814815E-4</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31"/>
       <c r="BT18" s="34"/>
       <c r="BU18" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV18" s="31"/>
       <c r="BW18" s="32"/>
       <c r="BX18" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BY18" s="31"/>
@@ -6903,57 +7017,63 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF18" s="31">
+      <c r="DF18" s="31"/>
+      <c r="DG18" s="34"/>
+      <c r="DH18" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI18" s="31">
         <v>1</v>
       </c>
-      <c r="DG18" s="34">
+      <c r="DJ18" s="34">
         <v>1.238425925925926E-2</v>
       </c>
-      <c r="DH18" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK18" s="33">
+        <f t="shared" si="26"/>
         <v>8.5995370370370375E-3</v>
       </c>
-      <c r="DI18" s="31"/>
-      <c r="DJ18" s="34"/>
-      <c r="DK18" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
-      </c>
-      <c r="DL18" s="31">
-        <v>1</v>
-      </c>
-      <c r="DM18" s="34">
-        <v>2.7743055555555556E-2</v>
-      </c>
-      <c r="DN18" s="33">
+      <c r="DL18" s="31"/>
+      <c r="DM18" s="34"/>
+      <c r="DN18" s="33" t="str">
         <f t="shared" si="27"/>
-        <v>2.3958333333333331E-2</v>
+        <v>NA</v>
       </c>
       <c r="DO18" s="31">
         <v>1</v>
       </c>
       <c r="DP18" s="34">
-        <v>6.0648148148148145E-3</v>
+        <v>2.7743055555555556E-2</v>
       </c>
       <c r="DQ18" s="33">
         <f t="shared" si="28"/>
+        <v>2.3958333333333331E-2</v>
+      </c>
+      <c r="DR18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS18" s="34">
+        <v>6.0648148148148145E-3</v>
+      </c>
+      <c r="DT18" s="33">
+        <f t="shared" si="29"/>
         <v>2.2800925925925922E-3</v>
-      </c>
-      <c r="DR18" s="31"/>
-      <c r="DS18" s="34"/>
-      <c r="DT18" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU18" s="31"/>
       <c r="DV18" s="34"/>
       <c r="DW18" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX18" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX18" s="31"/>
+      <c r="DY18" s="34"/>
+      <c r="DZ18" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA18" s="35"/>
     </row>
-    <row r="19" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>197</v>
       </c>
@@ -6970,7 +7090,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>E4</v>
       </c>
       <c r="G19" s="5">
@@ -7006,7 +7126,7 @@
         <v>4</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.8333333333333293E-2</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -7037,7 +7157,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.204861111111111E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -7047,7 +7167,7 @@
         <v>1.5659722222222221E-2</v>
       </c>
       <c r="AF19" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4.2048611111111113E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -7070,7 +7190,7 @@
         <v>4.4675925925925924E-3</v>
       </c>
       <c r="AN19" s="33">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.2731481481481448E-4</v>
       </c>
       <c r="AO19" s="31">
@@ -7080,7 +7200,7 @@
         <v>3.1550925925925927E-2</v>
       </c>
       <c r="AQ19" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.721064814814815E-2</v>
       </c>
       <c r="AR19" s="31">
@@ -7090,7 +7210,7 @@
         <v>4.417824074074074E-2</v>
       </c>
       <c r="AT19" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>3.9837962962962964E-2</v>
       </c>
       <c r="AU19" s="31">
@@ -7100,7 +7220,7 @@
         <v>7.2106481481481483E-3</v>
       </c>
       <c r="AW19" s="33">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.8703703703703703E-3</v>
       </c>
       <c r="AX19" s="31"/>
@@ -7122,19 +7242,19 @@
         <v>3.9594907407407405E-2</v>
       </c>
       <c r="BF19" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.5254629629629629E-2</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31"/>
       <c r="BK19" s="34"/>
       <c r="BL19" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="31">
@@ -7144,25 +7264,25 @@
         <v>1.125E-2</v>
       </c>
       <c r="BO19" s="33">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>6.9097222222222216E-3</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="34"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="31"/>
       <c r="BW19" s="32"/>
       <c r="BX19" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BY19" s="31"/>
@@ -7189,21 +7309,21 @@
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK19" s="31">
+      <c r="CK19" s="31"/>
+      <c r="CL19" s="34"/>
+      <c r="CM19" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN19" s="31">
         <v>1</v>
       </c>
-      <c r="CL19" s="34">
+      <c r="CO19" s="34">
         <v>8.6574074074074071E-3</v>
       </c>
-      <c r="CM19" s="33">
-        <f t="shared" si="18"/>
+      <c r="CP19" s="33">
+        <f t="shared" si="19"/>
         <v>4.3171296296296291E-3</v>
-      </c>
-      <c r="CN19" s="31"/>
-      <c r="CO19" s="34"/>
-      <c r="CP19" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
       </c>
       <c r="CQ19" s="31"/>
       <c r="CR19" s="34"/>
@@ -7235,57 +7355,63 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF19" s="31">
+      <c r="DF19" s="31"/>
+      <c r="DG19" s="34"/>
+      <c r="DH19" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI19" s="31">
         <v>1</v>
       </c>
-      <c r="DG19" s="34">
+      <c r="DJ19" s="34">
         <v>9.8379629629629633E-3</v>
       </c>
-      <c r="DH19" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK19" s="33">
+        <f t="shared" si="26"/>
         <v>5.4976851851851853E-3</v>
       </c>
-      <c r="DI19" s="31"/>
-      <c r="DJ19" s="34"/>
-      <c r="DK19" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
-      </c>
-      <c r="DL19" s="31">
+      <c r="DL19" s="31"/>
+      <c r="DM19" s="34"/>
+      <c r="DN19" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO19" s="31">
         <v>2</v>
       </c>
-      <c r="DM19" s="34">
+      <c r="DP19" s="34">
         <v>9.7337962962962959E-3</v>
-      </c>
-      <c r="DN19" s="33">
-        <f t="shared" si="27"/>
-        <v>5.393518518518518E-3</v>
-      </c>
-      <c r="DO19" s="31">
-        <v>1</v>
-      </c>
-      <c r="DP19" s="34">
-        <v>1.7777777777777778E-2</v>
       </c>
       <c r="DQ19" s="33">
         <f t="shared" si="28"/>
+        <v>5.393518518518518E-3</v>
+      </c>
+      <c r="DR19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS19" s="34">
+        <v>1.7777777777777778E-2</v>
+      </c>
+      <c r="DT19" s="33">
+        <f t="shared" si="29"/>
         <v>1.34375E-2</v>
-      </c>
-      <c r="DR19" s="31"/>
-      <c r="DS19" s="34"/>
-      <c r="DT19" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU19" s="31"/>
       <c r="DV19" s="34"/>
       <c r="DW19" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX19" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX19" s="31"/>
+      <c r="DY19" s="34"/>
+      <c r="DZ19" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA19" s="35"/>
     </row>
-    <row r="20" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>197</v>
       </c>
@@ -7302,7 +7428,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>E6</v>
       </c>
       <c r="G20" s="5">
@@ -7338,7 +7464,7 @@
         <v>3</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.6944444444444464E-2</v>
       </c>
       <c r="R20" s="6" t="s">
@@ -7367,7 +7493,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.3761574074074071E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -7375,7 +7501,7 @@
       </c>
       <c r="AE20" s="20"/>
       <c r="AF20" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.9039351851851846E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -7394,13 +7520,13 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="34"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31"/>
       <c r="AP20" s="34"/>
       <c r="AQ20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="31">
@@ -7410,13 +7536,13 @@
         <v>2.78125E-2</v>
       </c>
       <c r="AT20" s="33">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>2.3090277777777779E-2</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -7434,19 +7560,19 @@
       <c r="BD20" s="31"/>
       <c r="BE20" s="34"/>
       <c r="BF20" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31"/>
       <c r="BK20" s="34"/>
       <c r="BL20" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="31">
@@ -7456,19 +7582,19 @@
         <v>3.5439814814814813E-2</v>
       </c>
       <c r="BO20" s="33">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.0717592592592591E-2</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="31">
@@ -7478,7 +7604,7 @@
         <v>1.2314814814814815E-2</v>
       </c>
       <c r="BX20" s="33">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>7.5925925925925926E-3</v>
       </c>
       <c r="BY20" s="31"/>
@@ -7505,21 +7631,21 @@
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK20" s="31">
+      <c r="CK20" s="31"/>
+      <c r="CL20" s="34"/>
+      <c r="CM20" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN20" s="31">
         <v>1</v>
       </c>
-      <c r="CL20" s="34">
+      <c r="CO20" s="34">
         <v>8.1597222222222227E-3</v>
       </c>
-      <c r="CM20" s="33">
-        <f t="shared" si="18"/>
+      <c r="CP20" s="33">
+        <f t="shared" si="19"/>
         <v>3.4375000000000005E-3</v>
-      </c>
-      <c r="CN20" s="31"/>
-      <c r="CO20" s="34"/>
-      <c r="CP20" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
       </c>
       <c r="CQ20" s="31"/>
       <c r="CR20" s="34"/>
@@ -7551,21 +7677,21 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF20" s="31">
+      <c r="DF20" s="31"/>
+      <c r="DG20" s="34"/>
+      <c r="DH20" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI20" s="31">
         <v>1</v>
       </c>
-      <c r="DG20" s="34">
+      <c r="DJ20" s="34">
         <v>1.5868055555555555E-2</v>
       </c>
-      <c r="DH20" s="33">
-        <f t="shared" si="25"/>
+      <c r="DK20" s="33">
+        <f t="shared" si="26"/>
         <v>1.1145833333333334E-2</v>
-      </c>
-      <c r="DI20" s="31"/>
-      <c r="DJ20" s="34"/>
-      <c r="DK20" s="33" t="str">
-        <f t="shared" si="26"/>
-        <v>NA</v>
       </c>
       <c r="DL20" s="31"/>
       <c r="DM20" s="34"/>
@@ -7573,31 +7699,37 @@
         <f t="shared" si="27"/>
         <v>NA</v>
       </c>
-      <c r="DO20" s="31">
+      <c r="DO20" s="31"/>
+      <c r="DP20" s="34"/>
+      <c r="DQ20" s="33" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR20" s="31">
         <v>1</v>
       </c>
-      <c r="DP20" s="34">
+      <c r="DS20" s="34">
         <v>9.2245370370370363E-3</v>
       </c>
-      <c r="DQ20" s="33">
-        <f t="shared" si="28"/>
+      <c r="DT20" s="33">
+        <f t="shared" si="29"/>
         <v>4.502314814814814E-3</v>
-      </c>
-      <c r="DR20" s="31"/>
-      <c r="DS20" s="34"/>
-      <c r="DT20" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU20" s="31"/>
       <c r="DV20" s="34"/>
       <c r="DW20" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX20" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX20" s="31"/>
+      <c r="DY20" s="34"/>
+      <c r="DZ20" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA20" s="35"/>
     </row>
-    <row r="21" spans="1:128" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:131" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>197</v>
       </c>
@@ -7614,7 +7746,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="74" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>E5</v>
       </c>
       <c r="G21" s="5">
@@ -7650,7 +7782,7 @@
         <v>3</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.6250000000000022E-2</v>
       </c>
       <c r="R21" s="5" t="s">
@@ -7679,7 +7811,7 @@
       <c r="AA21" s="77"/>
       <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.821759259259259E-2</v>
       </c>
       <c r="AD21" s="78">
@@ -7689,7 +7821,7 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="AF21" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4.2604166666666665E-2</v>
       </c>
       <c r="AG21" s="21">
@@ -7708,25 +7840,25 @@
       <c r="AL21" s="31"/>
       <c r="AM21" s="32"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31"/>
       <c r="AP21" s="32"/>
       <c r="AQ21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -7744,19 +7876,19 @@
       <c r="BD21" s="31"/>
       <c r="BE21" s="34"/>
       <c r="BF21" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31"/>
       <c r="BK21" s="32"/>
       <c r="BL21" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM21" s="31">
@@ -7766,25 +7898,25 @@
         <v>1.0254629629629629E-2</v>
       </c>
       <c r="BO21" s="33">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>5.9143518518518512E-3</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31"/>
       <c r="BT21" s="32"/>
       <c r="BU21" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV21" s="31"/>
       <c r="BW21" s="32"/>
       <c r="BX21" s="33" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BY21" s="31"/>
@@ -7853,68 +7985,74 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF21" s="31">
+      <c r="DF21" s="31"/>
+      <c r="DG21" s="32"/>
+      <c r="DH21" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI21" s="31">
         <v>1</v>
       </c>
-      <c r="DG21" s="56">
+      <c r="DJ21" s="56">
         <v>1.361111111111111E-2</v>
-      </c>
-      <c r="DH21" s="33">
-        <f t="shared" si="25"/>
-        <v>9.2708333333333323E-3</v>
-      </c>
-      <c r="DI21" s="31">
-        <v>2</v>
-      </c>
-      <c r="DJ21" s="56">
-        <v>3.005787037037037E-2</v>
       </c>
       <c r="DK21" s="33">
         <f t="shared" si="26"/>
-        <v>2.5717592592592591E-2</v>
+        <v>9.2708333333333323E-3</v>
       </c>
       <c r="DL21" s="31">
-        <v>1</v>
-      </c>
-      <c r="DM21" s="34">
-        <v>2.554398148148148E-2</v>
+        <v>2</v>
+      </c>
+      <c r="DM21" s="56">
+        <v>3.005787037037037E-2</v>
       </c>
       <c r="DN21" s="33">
         <f t="shared" si="27"/>
-        <v>2.1203703703703704E-2</v>
+        <v>2.5717592592592591E-2</v>
       </c>
       <c r="DO21" s="31">
         <v>1</v>
       </c>
-      <c r="DP21" s="56">
-        <v>7.7314814814814815E-3</v>
+      <c r="DP21" s="34">
+        <v>2.554398148148148E-2</v>
       </c>
       <c r="DQ21" s="33">
         <f t="shared" si="28"/>
+        <v>2.1203703703703704E-2</v>
+      </c>
+      <c r="DR21" s="31">
+        <v>1</v>
+      </c>
+      <c r="DS21" s="56">
+        <v>7.7314814814814815E-3</v>
+      </c>
+      <c r="DT21" s="33">
+        <f t="shared" si="29"/>
         <v>3.3912037037037036E-3</v>
-      </c>
-      <c r="DR21" s="31"/>
-      <c r="DS21" s="56"/>
-      <c r="DT21" s="33" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
       </c>
       <c r="DU21" s="31"/>
       <c r="DV21" s="56"/>
       <c r="DW21" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX21" s="35"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX21" s="31"/>
+      <c r="DY21" s="56"/>
+      <c r="DZ21" s="33" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA21" s="35"/>
     </row>
-    <row r="22" spans="1:128" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:131" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="75" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="G22" s="11"/>
@@ -7934,7 +8072,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="R22" s="11"/>
@@ -7949,13 +8087,13 @@
       <c r="AA22" s="69"/>
       <c r="AB22" s="69"/>
       <c r="AC22" s="23">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AD22" s="80"/>
       <c r="AE22" s="80"/>
       <c r="AF22" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG22" s="24"/>
@@ -7966,25 +8104,25 @@
       <c r="AL22" s="38"/>
       <c r="AM22" s="40"/>
       <c r="AN22" s="41" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
       <c r="AQ22" s="41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="41" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
       <c r="AV22" s="82"/>
       <c r="AW22" s="41" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
@@ -8002,43 +8140,43 @@
       <c r="BD22" s="38"/>
       <c r="BE22" s="40"/>
       <c r="BF22" s="41" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="38"/>
       <c r="BH22" s="82"/>
       <c r="BI22" s="41" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38"/>
       <c r="BK22" s="82"/>
       <c r="BL22" s="41" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BM22" s="38"/>
       <c r="BN22" s="40"/>
       <c r="BO22" s="41" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BP22" s="38"/>
       <c r="BQ22" s="82"/>
       <c r="BR22" s="41" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
       <c r="BT22" s="82"/>
       <c r="BU22" s="41" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="38"/>
       <c r="BW22" s="82"/>
       <c r="BX22" s="41" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>NA</v>
       </c>
       <c r="BY22" s="38"/>
@@ -8090,7 +8228,7 @@
         <v>NA</v>
       </c>
       <c r="CW22" s="38"/>
-      <c r="CX22" s="40"/>
+      <c r="CX22" s="82"/>
       <c r="CY22" s="41" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
@@ -8140,10 +8278,16 @@
       <c r="DU22" s="38"/>
       <c r="DV22" s="40"/>
       <c r="DW22" s="41" t="str">
-        <f t="shared" si="46"/>
-        <v>NA</v>
-      </c>
-      <c r="DX22" s="39"/>
+        <f t="shared" si="30"/>
+        <v>NA</v>
+      </c>
+      <c r="DX22" s="38"/>
+      <c r="DY22" s="40"/>
+      <c r="DZ22" s="41" t="str">
+        <f t="shared" si="47"/>
+        <v>NA</v>
+      </c>
+      <c r="EA22" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/URUVS/Datasheets/URUV/08.2024/August_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/08.2024/August_RecordingData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\08.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC1D5B3-3CD8-46A1-8735-81253A1BA885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9AFA1E-8503-46C4-9820-A4A9F5B93D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -671,9 +671,6 @@
     <t>T1_FISHO</t>
   </si>
   <si>
-    <t>MAXN_FISHCHEETAGIRLZ</t>
-  </si>
-  <si>
     <t>TIME_1STCHEETAGIRLZ</t>
   </si>
   <si>
@@ -723,6 +720,9 @@
   </si>
   <si>
     <t>T1_FISHBT</t>
+  </si>
+  <si>
+    <t>MAXN_CHEETAGIRLZ</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1077,7 @@
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="21" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1656,13 +1656,13 @@
         <v>209</v>
       </c>
       <c r="CK1" s="81" t="s">
+        <v>224</v>
+      </c>
+      <c r="CL1" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="CL1" s="27" t="s">
+      <c r="CM1" s="59" t="s">
         <v>226</v>
-      </c>
-      <c r="CM1" s="59" t="s">
-        <v>227</v>
       </c>
       <c r="CN1" s="81" t="s">
         <v>123</v>
@@ -1701,13 +1701,13 @@
         <v>66</v>
       </c>
       <c r="CZ1" s="81" t="s">
+        <v>227</v>
+      </c>
+      <c r="DA1" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="DA1" s="27" t="s">
+      <c r="DB1" s="59" t="s">
         <v>211</v>
-      </c>
-      <c r="DB1" s="59" t="s">
-        <v>212</v>
       </c>
       <c r="DC1" s="81" t="s">
         <v>141</v>
@@ -1746,40 +1746,40 @@
         <v>33</v>
       </c>
       <c r="DO1" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="DP1" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="DP1" s="27" t="s">
+      <c r="DQ1" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="DQ1" s="59" t="s">
+      <c r="DR1" s="81" t="s">
         <v>215</v>
       </c>
-      <c r="DR1" s="81" t="s">
+      <c r="DS1" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="DS1" s="27" t="s">
+      <c r="DT1" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="DT1" s="59" t="s">
+      <c r="DU1" s="81" t="s">
         <v>218</v>
       </c>
-      <c r="DU1" s="81" t="s">
+      <c r="DV1" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="DV1" s="27" t="s">
+      <c r="DW1" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="DW1" s="59" t="s">
+      <c r="DX1" s="81" t="s">
         <v>221</v>
       </c>
-      <c r="DX1" s="81" t="s">
+      <c r="DY1" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="DY1" s="27" t="s">
+      <c r="DZ1" s="59" t="s">
         <v>223</v>
-      </c>
-      <c r="DZ1" s="59" t="s">
-        <v>224</v>
       </c>
       <c r="EA1" s="28" t="s">
         <v>31</v>
@@ -6864,7 +6864,7 @@
         <v>NA</v>
       </c>
       <c r="AO18" s="87">
-        <v>4.1087962962962962E-3</v>
+        <v>2</v>
       </c>
       <c r="AP18" s="34">
         <v>6.4004629629629628E-3</v>
